--- a/tests/fixtures/manager/MANAGER_FULLNAME.xlsx
+++ b/tests/fixtures/manager/MANAGER_FULLNAME.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3464,6 +3464,534 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>景顺长城</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>景顺长城基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>中欧</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>中欧基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>华泰保兴</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>华泰保兴基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>万家</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>万家基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>中泰</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>中泰证券(上海)资产管理有限公司</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>华商</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>华商基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>交银施罗德</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>交银施罗德基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>中邮</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>中邮创业基金管理股份有限公司</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>西部利得</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>西部利得基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>宝盈</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>宝盈基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>建信</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>建信基金管理有限责任公司</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>汇丰晋信</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>汇丰晋信基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>招商</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>招商基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>富国</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>富国基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>融通</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>融通基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>东方添益债券</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>东方基金管理股份有限公司</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>恒生股息</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>博时基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>工业有色</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>万家基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>十年国债</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>国泰基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>科创芯片</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>嘉实基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>A500基金</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>华泰柏瑞基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>稀土基金</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>嘉实基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>电子龙头</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>富国基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>稀有金属</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>嘉实基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
